--- a/data.xlsx
+++ b/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThisPC\PycharmProjects\Tool_reg_hotmail_Demo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\Tool_reg_hotmail_Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CF1286-9EC2-4E32-BBB7-1103BA65CFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="363">
   <si>
     <t>1/username</t>
   </si>
@@ -61,9 +62,6 @@
   </si>
   <si>
     <t>Hoa</t>
-  </si>
-  <si>
-    <t>115.76.45.141:15125</t>
   </si>
   <si>
     <t>romantic_feynman5</t>
@@ -1116,7 +1114,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -1193,7 +1191,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 3" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1470,20 +1468,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" customWidth="1"/>
-    <col min="10" max="10" width="38.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.1796875" customWidth="1"/>
+    <col min="9" max="9" width="19.81640625" customWidth="1"/>
+    <col min="10" max="10" width="38.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" customHeight="1">
@@ -1532,28 +1530,26 @@
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="F2" s="5"/>
       <c r="G2" s="4">
         <v>37680</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="4">
@@ -1562,19 +1558,19 @@
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="4">
@@ -1583,19 +1579,19 @@
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="4">
@@ -1604,19 +1600,19 @@
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="4">
@@ -1625,19 +1621,19 @@
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="4">
@@ -1646,19 +1642,19 @@
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="4">
@@ -1667,19 +1663,19 @@
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="4">
@@ -1688,19 +1684,19 @@
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" t="s">
         <v>44</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="4">
@@ -1709,19 +1705,19 @@
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" t="s">
         <v>48</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="4">
@@ -1730,19 +1726,19 @@
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="4">
@@ -1751,19 +1747,19 @@
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" t="s">
         <v>56</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="4">
@@ -1772,19 +1768,19 @@
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" t="s">
         <v>60</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="4">
@@ -1793,19 +1789,19 @@
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" t="s">
         <v>64</v>
       </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="4">
@@ -1814,19 +1810,19 @@
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1">
       <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" t="s">
         <v>67</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="4">
@@ -1835,19 +1831,19 @@
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" t="s">
         <v>71</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="4">
@@ -1856,19 +1852,19 @@
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" t="s">
         <v>75</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="4">
@@ -1877,19 +1873,19 @@
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" t="s">
         <v>79</v>
       </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="4">
@@ -1898,19 +1894,19 @@
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" t="s">
         <v>82</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="4">
@@ -1919,19 +1915,19 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" t="s">
         <v>86</v>
       </c>
-      <c r="D21" t="s">
-        <v>87</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="4">
@@ -1940,19 +1936,19 @@
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" t="s">
         <v>89</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="4">
@@ -1961,19 +1957,19 @@
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" t="s">
         <v>93</v>
       </c>
-      <c r="D23" t="s">
-        <v>94</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="4">
@@ -1982,19 +1978,19 @@
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" t="s">
         <v>96</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="4">
@@ -2003,19 +1999,19 @@
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" t="s">
         <v>100</v>
       </c>
-      <c r="D25" t="s">
-        <v>101</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="4">
@@ -2024,19 +2020,19 @@
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" t="s">
         <v>103</v>
       </c>
-      <c r="D26" t="s">
-        <v>104</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="4">
@@ -2045,19 +2041,19 @@
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" t="s">
         <v>106</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="4">
@@ -2066,19 +2062,19 @@
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" t="s">
         <v>110</v>
       </c>
-      <c r="D28" t="s">
-        <v>111</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="4">
@@ -2087,19 +2083,19 @@
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" t="s">
         <v>113</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="4">
@@ -2108,19 +2104,19 @@
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" t="s">
         <v>117</v>
       </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
       <c r="E30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="4">
@@ -2129,19 +2125,19 @@
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" t="s">
         <v>120</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="4">
@@ -2150,19 +2146,19 @@
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" t="s">
         <v>124</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="4">
@@ -2171,19 +2167,19 @@
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" t="s">
         <v>128</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="4">
@@ -2192,19 +2188,19 @@
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" t="s">
         <v>132</v>
       </c>
-      <c r="D34" t="s">
-        <v>133</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="4">
@@ -2213,19 +2209,19 @@
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1">
       <c r="A35" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" t="s">
         <v>135</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="4">
@@ -2234,19 +2230,19 @@
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1">
       <c r="A36" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" t="s">
         <v>139</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="4">
@@ -2255,19 +2251,19 @@
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1">
       <c r="A37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" t="s">
         <v>143</v>
       </c>
-      <c r="D37" t="s">
-        <v>144</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="4">
@@ -2276,19 +2272,19 @@
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1">
       <c r="A38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" t="s">
         <v>146</v>
       </c>
-      <c r="D38" t="s">
-        <v>147</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="4">
@@ -2297,19 +2293,19 @@
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1">
       <c r="A39" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" t="s">
         <v>149</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="4">
@@ -2318,19 +2314,19 @@
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1">
       <c r="A40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B40" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" t="s">
         <v>153</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="4">
@@ -2339,19 +2335,19 @@
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1">
       <c r="A41" t="s">
+        <v>155</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" t="s">
         <v>157</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="4">
@@ -2360,19 +2356,19 @@
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1">
       <c r="A42" t="s">
+        <v>159</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B42" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" t="s">
         <v>161</v>
       </c>
-      <c r="D42" t="s">
-        <v>162</v>
-      </c>
       <c r="E42" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="4">
@@ -2381,19 +2377,19 @@
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1">
       <c r="A43" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" t="s">
         <v>164</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="4">
@@ -2402,19 +2398,19 @@
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1">
       <c r="A44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" t="s">
+        <v>100</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="D44" t="s">
-        <v>101</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="4">
@@ -2423,19 +2419,19 @@
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1">
       <c r="A45" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" t="s">
         <v>171</v>
       </c>
-      <c r="D45" t="s">
-        <v>172</v>
-      </c>
       <c r="E45" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="4">
@@ -2444,19 +2440,19 @@
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1">
       <c r="A46" t="s">
+        <v>172</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B46" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" t="s">
         <v>174</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="4">
@@ -2465,19 +2461,19 @@
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1">
       <c r="A47" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" t="s">
         <v>178</v>
       </c>
-      <c r="D47" t="s">
-        <v>179</v>
-      </c>
       <c r="E47" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="4">
@@ -2486,19 +2482,19 @@
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1">
       <c r="A48" t="s">
+        <v>179</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" t="s">
         <v>181</v>
       </c>
-      <c r="D48" t="s">
-        <v>182</v>
-      </c>
       <c r="E48" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="4">
@@ -2507,19 +2503,19 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B49" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" t="s">
         <v>184</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="4">
@@ -2528,19 +2524,19 @@
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
       <c r="A50" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" t="s">
         <v>188</v>
       </c>
-      <c r="D50" t="s">
-        <v>189</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="4">
@@ -2549,19 +2545,19 @@
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
       <c r="A51" t="s">
+        <v>189</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B51" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" t="s">
         <v>191</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="4">
@@ -2570,19 +2566,19 @@
     </row>
     <row r="52" spans="1:7" ht="15.75" customHeight="1">
       <c r="A52" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B52" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" t="s">
         <v>195</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="4">
@@ -2591,19 +2587,19 @@
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1">
       <c r="A53" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B53" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" t="s">
         <v>199</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="4">
@@ -2612,19 +2608,19 @@
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
       <c r="A54" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" t="s">
         <v>203</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="4">
@@ -2633,19 +2629,19 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1">
       <c r="A55" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B55" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" t="s">
         <v>207</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="4">
@@ -2654,19 +2650,19 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
       <c r="A56" t="s">
+        <v>209</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B56" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" t="s">
         <v>211</v>
       </c>
-      <c r="D56" t="s">
-        <v>212</v>
-      </c>
       <c r="E56" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="4">
@@ -2675,19 +2671,19 @@
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
       <c r="A57" t="s">
+        <v>212</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" t="s">
         <v>214</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="4">
@@ -2696,19 +2692,19 @@
     </row>
     <row r="58" spans="1:7" ht="15.75" customHeight="1">
       <c r="A58" t="s">
+        <v>216</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B58" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" t="s">
         <v>218</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="4">
@@ -2717,19 +2713,19 @@
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1">
       <c r="A59" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B59" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" t="s">
         <v>222</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="4">
@@ -2738,19 +2734,19 @@
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1">
       <c r="A60" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B60" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" t="s">
         <v>226</v>
       </c>
-      <c r="D60" t="s">
-        <v>227</v>
-      </c>
       <c r="E60" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="4">
@@ -2759,19 +2755,19 @@
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
       <c r="A61" t="s">
+        <v>227</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B61" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" t="s">
         <v>229</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="4">
@@ -2780,19 +2776,19 @@
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
       <c r="A62" t="s">
+        <v>231</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B62" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" t="s">
         <v>233</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="4">
@@ -2801,19 +2797,19 @@
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1">
       <c r="A63" t="s">
+        <v>235</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="D63" t="s">
         <v>237</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="4">
@@ -2822,19 +2818,19 @@
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1">
       <c r="A64" t="s">
+        <v>239</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B64" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="D64" t="s">
         <v>241</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="4">
@@ -2843,19 +2839,19 @@
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1">
       <c r="A65" t="s">
+        <v>243</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B65" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="D65" t="s">
         <v>245</v>
       </c>
-      <c r="D65" t="s">
-        <v>246</v>
-      </c>
       <c r="E65" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="4">
@@ -2864,19 +2860,19 @@
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1">
       <c r="A66" t="s">
+        <v>246</v>
+      </c>
+      <c r="B66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B66" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" t="s">
         <v>248</v>
       </c>
-      <c r="D66" t="s">
-        <v>249</v>
-      </c>
       <c r="E66" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="4">
@@ -2885,19 +2881,19 @@
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1">
       <c r="A67" t="s">
+        <v>249</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B67" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" t="s">
         <v>251</v>
       </c>
-      <c r="D67" t="s">
-        <v>252</v>
-      </c>
       <c r="E67" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="4">
@@ -2906,19 +2902,19 @@
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1">
       <c r="A68" t="s">
+        <v>252</v>
+      </c>
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B68" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" t="s">
         <v>254</v>
       </c>
-      <c r="D68" t="s">
-        <v>255</v>
-      </c>
       <c r="E68" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="4">
@@ -2927,19 +2923,19 @@
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1">
       <c r="A69" t="s">
+        <v>255</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" t="s">
         <v>257</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="4">
@@ -2948,19 +2944,19 @@
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1">
       <c r="A70" t="s">
+        <v>259</v>
+      </c>
+      <c r="B70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B70" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" t="s">
         <v>261</v>
       </c>
-      <c r="D70" t="s">
-        <v>262</v>
-      </c>
       <c r="E70" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="4">
@@ -2969,19 +2965,19 @@
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1">
       <c r="A71" t="s">
+        <v>262</v>
+      </c>
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B71" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" t="s">
         <v>264</v>
       </c>
-      <c r="D71" t="s">
-        <v>265</v>
-      </c>
       <c r="E71" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="4">
@@ -2990,19 +2986,19 @@
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1">
       <c r="A72" t="s">
+        <v>265</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B72" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" t="s">
         <v>267</v>
       </c>
-      <c r="D72" t="s">
-        <v>268</v>
-      </c>
       <c r="E72" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="4">
@@ -3011,19 +3007,19 @@
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1">
       <c r="A73" t="s">
+        <v>268</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B73" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" t="s">
         <v>270</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="4">
@@ -3032,19 +3028,19 @@
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1">
       <c r="A74" t="s">
+        <v>272</v>
+      </c>
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="D74" t="s">
         <v>274</v>
       </c>
-      <c r="D74" t="s">
-        <v>275</v>
-      </c>
       <c r="E74" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="4">
@@ -3053,19 +3049,19 @@
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1">
       <c r="A75" t="s">
+        <v>275</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B75" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" t="s">
         <v>277</v>
       </c>
-      <c r="D75" t="s">
-        <v>278</v>
-      </c>
       <c r="E75" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="4">
@@ -3074,19 +3070,19 @@
     </row>
     <row r="76" spans="1:7" ht="15.75" customHeight="1">
       <c r="A76" t="s">
+        <v>278</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B76" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" t="s">
         <v>280</v>
       </c>
-      <c r="D76" t="s">
-        <v>281</v>
-      </c>
       <c r="E76" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="4">
@@ -3095,19 +3091,19 @@
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1">
       <c r="A77" t="s">
+        <v>281</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B77" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" t="s">
+        <v>277</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="D77" t="s">
-        <v>278</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="4">
@@ -3116,19 +3112,19 @@
     </row>
     <row r="78" spans="1:7" ht="15.75" customHeight="1">
       <c r="A78" t="s">
+        <v>284</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B78" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="D78" t="s">
         <v>286</v>
       </c>
-      <c r="D78" t="s">
-        <v>287</v>
-      </c>
       <c r="E78" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="4">
@@ -3137,19 +3133,19 @@
     </row>
     <row r="79" spans="1:7" ht="15.75" customHeight="1">
       <c r="A79" t="s">
+        <v>287</v>
+      </c>
+      <c r="B79" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B79" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="2" t="s">
+      <c r="D79" t="s">
         <v>289</v>
       </c>
-      <c r="D79" t="s">
-        <v>290</v>
-      </c>
       <c r="E79" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="4">
@@ -3158,19 +3154,19 @@
     </row>
     <row r="80" spans="1:7" ht="15.75" customHeight="1">
       <c r="A80" t="s">
+        <v>290</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="2" t="s">
+      <c r="D80" t="s">
         <v>292</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="4">
@@ -3179,19 +3175,19 @@
     </row>
     <row r="81" spans="1:7" ht="15.75" customHeight="1">
       <c r="A81" t="s">
+        <v>294</v>
+      </c>
+      <c r="B81" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B81" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="D81" t="s">
+        <v>277</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="D81" t="s">
-        <v>278</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="4">
@@ -3200,19 +3196,19 @@
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1">
       <c r="A82" t="s">
+        <v>297</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="2" t="s">
+      <c r="D82" t="s">
         <v>299</v>
       </c>
-      <c r="D82" t="s">
-        <v>300</v>
-      </c>
       <c r="E82" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="4">
@@ -3221,19 +3217,19 @@
     </row>
     <row r="83" spans="1:7" ht="15.75" customHeight="1">
       <c r="A83" t="s">
+        <v>300</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B83" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" s="2" t="s">
+      <c r="D83" t="s">
         <v>302</v>
       </c>
-      <c r="D83" t="s">
-        <v>303</v>
-      </c>
       <c r="E83" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="4">
@@ -3242,19 +3238,19 @@
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1">
       <c r="A84" t="s">
+        <v>303</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="D84" t="s">
         <v>305</v>
       </c>
-      <c r="D84" t="s">
-        <v>306</v>
-      </c>
       <c r="E84" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="4">
@@ -3263,19 +3259,19 @@
     </row>
     <row r="85" spans="1:7" ht="15.75" customHeight="1">
       <c r="A85" t="s">
+        <v>306</v>
+      </c>
+      <c r="B85" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B85" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="2" t="s">
+      <c r="D85" t="s">
         <v>308</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="4">
@@ -3284,19 +3280,19 @@
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1">
       <c r="A86" t="s">
+        <v>310</v>
+      </c>
+      <c r="B86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B86" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="2" t="s">
+      <c r="D86" t="s">
         <v>312</v>
       </c>
-      <c r="D86" t="s">
-        <v>313</v>
-      </c>
       <c r="E86" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="4">
@@ -3305,19 +3301,19 @@
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1">
       <c r="A87" t="s">
+        <v>313</v>
+      </c>
+      <c r="B87" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B87" t="s">
-        <v>10</v>
-      </c>
-      <c r="C87" s="2" t="s">
+      <c r="D87" t="s">
         <v>315</v>
       </c>
-      <c r="D87" t="s">
-        <v>316</v>
-      </c>
       <c r="E87" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="4">
@@ -3326,19 +3322,19 @@
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1">
       <c r="A88" t="s">
+        <v>316</v>
+      </c>
+      <c r="B88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B88" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" t="s">
         <v>318</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="4">
@@ -3347,19 +3343,19 @@
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1">
       <c r="A89" t="s">
+        <v>320</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B89" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" s="2" t="s">
+      <c r="D89" t="s">
         <v>322</v>
       </c>
-      <c r="D89" t="s">
-        <v>323</v>
-      </c>
       <c r="E89" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="4">
@@ -3368,19 +3364,19 @@
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1">
       <c r="A90" t="s">
+        <v>323</v>
+      </c>
+      <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B90" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="2" t="s">
+      <c r="D90" t="s">
         <v>325</v>
       </c>
-      <c r="D90" t="s">
-        <v>326</v>
-      </c>
       <c r="E90" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="4">
@@ -3389,19 +3385,19 @@
     </row>
     <row r="91" spans="1:7" ht="15.75" customHeight="1">
       <c r="A91" t="s">
+        <v>326</v>
+      </c>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B91" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="D91" t="s">
         <v>328</v>
       </c>
-      <c r="D91" t="s">
-        <v>329</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="4">
@@ -3410,19 +3406,19 @@
     </row>
     <row r="92" spans="1:7" ht="15.75" customHeight="1">
       <c r="A92" t="s">
+        <v>329</v>
+      </c>
+      <c r="B92" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B92" t="s">
-        <v>10</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="D92" t="s">
         <v>331</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="4">
@@ -3431,19 +3427,19 @@
     </row>
     <row r="93" spans="1:7" ht="15.75" customHeight="1">
       <c r="A93" t="s">
+        <v>333</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B93" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" s="2" t="s">
+      <c r="D93" t="s">
         <v>335</v>
       </c>
-      <c r="D93" t="s">
-        <v>336</v>
-      </c>
       <c r="E93" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="4">
@@ -3452,19 +3448,19 @@
     </row>
     <row r="94" spans="1:7" ht="15.75" customHeight="1">
       <c r="A94" t="s">
+        <v>336</v>
+      </c>
+      <c r="B94" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B94" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="2" t="s">
+      <c r="D94" t="s">
         <v>338</v>
       </c>
-      <c r="D94" t="s">
-        <v>339</v>
-      </c>
       <c r="E94" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="4">
@@ -3473,19 +3469,19 @@
     </row>
     <row r="95" spans="1:7" ht="15.75" customHeight="1">
       <c r="A95" t="s">
+        <v>339</v>
+      </c>
+      <c r="B95" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B95" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" s="2" t="s">
+      <c r="D95" t="s">
         <v>341</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="4">
@@ -3494,19 +3490,19 @@
     </row>
     <row r="96" spans="1:7" ht="15.75" customHeight="1">
       <c r="A96" t="s">
+        <v>343</v>
+      </c>
+      <c r="B96" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B96" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="D96" t="s">
         <v>345</v>
       </c>
-      <c r="D96" t="s">
-        <v>346</v>
-      </c>
       <c r="E96" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="4">
@@ -3515,19 +3511,19 @@
     </row>
     <row r="97" spans="1:7" ht="15.75" customHeight="1">
       <c r="A97" t="s">
+        <v>346</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B97" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="D97" t="s">
         <v>348</v>
       </c>
-      <c r="D97" t="s">
-        <v>349</v>
-      </c>
       <c r="E97" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="4">
@@ -3536,19 +3532,19 @@
     </row>
     <row r="98" spans="1:7" ht="15.75" customHeight="1">
       <c r="A98" t="s">
+        <v>349</v>
+      </c>
+      <c r="B98" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B98" t="s">
-        <v>10</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="D98" t="s">
         <v>351</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="4">
@@ -3557,19 +3553,19 @@
     </row>
     <row r="99" spans="1:7" ht="15.75" customHeight="1">
       <c r="A99" t="s">
+        <v>353</v>
+      </c>
+      <c r="B99" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B99" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" s="2" t="s">
+      <c r="D99" t="s">
         <v>355</v>
       </c>
-      <c r="D99" t="s">
-        <v>356</v>
-      </c>
       <c r="E99" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="4">
@@ -3578,19 +3574,19 @@
     </row>
     <row r="100" spans="1:7" ht="15.75" customHeight="1">
       <c r="A100" t="s">
+        <v>356</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B100" t="s">
-        <v>10</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="D100" t="s">
         <v>358</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="4">
@@ -3599,19 +3595,19 @@
     </row>
     <row r="101" spans="1:7" ht="15.75" customHeight="1">
       <c r="A101" t="s">
+        <v>360</v>
+      </c>
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B101" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" s="2" t="s">
+      <c r="D101" t="s">
         <v>362</v>
       </c>
-      <c r="D101" t="s">
-        <v>363</v>
-      </c>
       <c r="E101" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="4">
